--- a/Documents/仕様書.xlsx
+++ b/Documents/仕様書.xlsx
@@ -5,20 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2316012\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2316012\Documents\AvilityProject\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772BDD34-8DA6-4679-9C7A-27BEBD28D2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E798D614-8332-4A73-B4BE-152425C01D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5265" yWindow="4185" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="1" r:id="rId1"/>
     <sheet name="アビリティ" sheetId="5" r:id="rId2"/>
-    <sheet name="プレイヤー操作" sheetId="6" r:id="rId3"/>
-    <sheet name="クラス図" sheetId="4" r:id="rId4"/>
-    <sheet name="ステージ構成" sheetId="2" r:id="rId5"/>
-    <sheet name="画面遷移" sheetId="3" r:id="rId6"/>
+    <sheet name="パラメータ関係" sheetId="7" r:id="rId3"/>
+    <sheet name="プレイヤー操作" sheetId="6" r:id="rId4"/>
+    <sheet name="クラス図" sheetId="4" r:id="rId5"/>
+    <sheet name="ステージ構成" sheetId="2" r:id="rId6"/>
+    <sheet name="画面遷移" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="119">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -422,12 +423,202 @@
     <t>https://miro.com/app/live-embed/uXjVGj5v6-4=/?moveToViewport=-2715%2C-2146%2C6062%2C2819&amp;embedId=110213163200</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>アビリティ：スタンプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：ボックス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー(Lv.1)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー(Lv.2)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー(Lv.3)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力上昇率</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ジョウショウリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵：クローン</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加攻撃値</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>コウゲキアタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのステータスに加える</t>
+    <rPh sb="12" eb="13">
+      <t>クワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：ショット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>種類</t>
+    <rPh sb="0" eb="2">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オブジェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>能力</t>
+    <rPh sb="0" eb="2">
+      <t>ノウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎ステータスが上昇する</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのステータスに加える
+壁に反射するたびに攻撃力上昇率を0.1%ずつ上げていく</t>
+    <rPh sb="12" eb="13">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハンシャ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>ジョウショウリツ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：エアースラッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飛び道具</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ドウグ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのステータスに加える
+ダメージはプレイヤーの攻撃力から参照する</t>
+    <rPh sb="12" eb="13">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：テレポート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オブジェクト：キャラクターか敵、
+能力：アビリティ、
+飛び道具：魔法系の攻撃</t>
+    <rPh sb="14" eb="15">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ドウグ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,6 +646,15 @@
       <color theme="0"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -490,7 +690,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -513,13 +713,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -546,6 +761,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -3003,6 +3227,384 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24BB326-7754-4978-971A-09FA9DBDB891}">
+  <dimension ref="C2:K26"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="8.125" customWidth="1"/>
+    <col min="3" max="3" width="8.875" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="36.625" customWidth="1"/>
+    <col min="8" max="8" width="9.375" customWidth="1"/>
+    <col min="9" max="9" width="10.75" customWidth="1"/>
+    <col min="10" max="10" width="12.625" customWidth="1"/>
+    <col min="11" max="11" width="53.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="5:11" ht="34.5" customHeight="1"/>
+    <row r="3" spans="5:11" ht="56.25">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="5:11">
+      <c r="E4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="5:11">
+      <c r="E5" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="11">
+        <v>100</v>
+      </c>
+      <c r="H5" s="11">
+        <v>50</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0</v>
+      </c>
+      <c r="J5" s="11">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11"/>
+    </row>
+    <row r="6" spans="5:11">
+      <c r="E6" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" s="11">
+        <v>140</v>
+      </c>
+      <c r="H6" s="11">
+        <v>70</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0</v>
+      </c>
+      <c r="J6" s="11">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="5:11">
+      <c r="E7" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" s="11">
+        <v>180</v>
+      </c>
+      <c r="H7" s="11">
+        <v>90</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0</v>
+      </c>
+      <c r="J7" s="11">
+        <v>0</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="5:11">
+      <c r="E8" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" s="11">
+        <v>75</v>
+      </c>
+      <c r="H8" s="11">
+        <v>10</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0</v>
+      </c>
+      <c r="K8" s="11"/>
+    </row>
+    <row r="9" spans="5:11">
+      <c r="E9" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="11">
+        <v>50</v>
+      </c>
+      <c r="J9" s="11">
+        <v>0</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="5:11" ht="37.5">
+      <c r="E10" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="11">
+        <v>1</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>100</v>
+      </c>
+      <c r="J10" s="11">
+        <v>0</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="5:11" ht="37.5">
+      <c r="E11" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I11" s="11">
+        <v>20</v>
+      </c>
+      <c r="J11" s="11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="5:11" ht="37.5">
+      <c r="E12" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I12" s="11">
+        <v>30</v>
+      </c>
+      <c r="J12" s="11">
+        <v>0</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="5:11">
+      <c r="E13" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="11">
+        <v>30</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="5:11">
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+    </row>
+    <row r="15" spans="5:11">
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+    </row>
+    <row r="16" spans="5:11">
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+    </row>
+    <row r="17" spans="5:11">
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+    </row>
+    <row r="18" spans="5:11">
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+    </row>
+    <row r="19" spans="5:11">
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+    </row>
+    <row r="20" spans="5:11">
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+    </row>
+    <row r="21" spans="5:11">
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+    </row>
+    <row r="22" spans="5:11">
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+    </row>
+    <row r="23" spans="5:11">
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+    </row>
+    <row r="24" spans="5:11">
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+    </row>
+    <row r="25" spans="5:11">
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+    </row>
+    <row r="26" spans="5:11">
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E95FD20-A5A3-4B15-92BD-87102E0D51C4}">
   <dimension ref="D4:H19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3254,7 +3856,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53FD8591-C896-4DE4-A6F4-2E97EA0E58D4}">
   <dimension ref="C6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3277,7 +3879,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63FD3BE4-D508-4233-B771-14B3707C8539}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3287,7 +3889,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44CE8C6D-A5D9-4296-ADEE-7D23BF1A189A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3299,6 +3901,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896">
@@ -3307,15 +3918,6 @@
     <TaxCatchAll xmlns="4df1b71f-4a55-4669-b731-80afe8527666" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3500,20 +4102,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44FA154F-6742-4FF5-B2DD-F9D58013581C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
     <ds:schemaRef ds:uri="4df1b71f-4a55-4669-b731-80afe8527666"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Documents/仕様書.xlsx
+++ b/Documents/仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2316012\Documents\AvilityProject\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E798D614-8332-4A73-B4BE-152425C01D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC676899-23C5-4536-8D78-FEA1343A3093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5265" yWindow="4185" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="120">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -611,6 +611,10 @@
     <rPh sb="36" eb="38">
       <t>コウゲキ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：メタル</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3228,7 +3232,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24BB326-7754-4978-971A-09FA9DBDB891}">
-  <dimension ref="C2:K26"/>
+  <dimension ref="E2:K26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="8.125" customWidth="1"/>
@@ -3481,9 +3485,15 @@
       </c>
     </row>
     <row r="14" spans="5:11">
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
+      <c r="E14" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>108</v>
+      </c>
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
@@ -3901,26 +3911,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4df1b71f-4a55-4669-b731-80afe8527666" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A266895D3745634495530F4DE8F2682A" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="bc4232d39cbd51ad980f2da95d792baf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896" xmlns:ns3="4df1b71f-4a55-4669-b731-80afe8527666" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dce5d8306af64726948b5c30825d92f7" ns2:_="" ns3:_="">
     <xsd:import namespace="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
@@ -4101,10 +4091,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4df1b71f-4a55-4669-b731-80afe8527666" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4AFE8B2-255C-4B8A-97FA-8FA1BCDB4ABE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
+    <ds:schemaRef ds:uri="4df1b71f-4a55-4669-b731-80afe8527666"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4121,20 +4142,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4AFE8B2-255C-4B8A-97FA-8FA1BCDB4ABE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
-    <ds:schemaRef ds:uri="4df1b71f-4a55-4669-b731-80afe8527666"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Documents/仕様書.xlsx
+++ b/Documents/仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2316012\Documents\AvilityProject\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC676899-23C5-4536-8D78-FEA1343A3093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D49336-8EDE-4A03-84E0-0D6A9D755173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5265" yWindow="4185" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="124">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -615,6 +615,34 @@
   </si>
   <si>
     <t>アビリティ：メタル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重力</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重力上昇率</t>
+    <rPh sb="0" eb="5">
+      <t>ジュウリョクジョウショウリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのステータスに一時的に加える</t>
+    <rPh sb="12" eb="15">
+      <t>イチジテキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>クワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -738,7 +766,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -773,6 +801,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3232,7 +3263,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24BB326-7754-4978-971A-09FA9DBDB891}">
-  <dimension ref="E2:K26"/>
+  <dimension ref="E2:M26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="8.125" customWidth="1"/>
@@ -3242,12 +3273,12 @@
     <col min="6" max="6" width="36.625" customWidth="1"/>
     <col min="8" max="8" width="9.375" customWidth="1"/>
     <col min="9" max="9" width="10.75" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="11" width="53.75" customWidth="1"/>
+    <col min="10" max="12" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="53.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:11" ht="34.5" customHeight="1"/>
-    <row r="3" spans="5:11" ht="56.25">
+    <row r="2" spans="5:13" ht="34.5" customHeight="1"/>
+    <row r="3" spans="5:13" ht="56.25">
       <c r="E3" s="7"/>
       <c r="F3" s="8" t="s">
         <v>118</v>
@@ -3257,8 +3288,10 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="5:11">
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" spans="5:13">
       <c r="E4" s="10" t="s">
         <v>0</v>
       </c>
@@ -3278,10 +3311,16 @@
         <v>102</v>
       </c>
       <c r="K4" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="M4" s="10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="5:11">
+    <row r="5" spans="5:13">
       <c r="E5" s="11" t="s">
         <v>98</v>
       </c>
@@ -3300,9 +3339,15 @@
       <c r="J5" s="11">
         <v>0</v>
       </c>
-      <c r="K5" s="11"/>
-    </row>
-    <row r="6" spans="5:11">
+      <c r="K5" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L5" s="11">
+        <v>0</v>
+      </c>
+      <c r="M5" s="11"/>
+    </row>
+    <row r="6" spans="5:13">
       <c r="E6" s="11" t="s">
         <v>99</v>
       </c>
@@ -3321,11 +3366,17 @@
       <c r="J6" s="11">
         <v>0</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L6" s="11">
+        <v>0</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="5:11">
+    <row r="7" spans="5:13">
       <c r="E7" s="11" t="s">
         <v>100</v>
       </c>
@@ -3344,11 +3395,17 @@
       <c r="J7" s="11">
         <v>0</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="5:11">
+    <row r="8" spans="5:13">
       <c r="E8" s="11" t="s">
         <v>103</v>
       </c>
@@ -3367,9 +3424,15 @@
       <c r="J8" s="11">
         <v>0</v>
       </c>
-      <c r="K8" s="11"/>
-    </row>
-    <row r="9" spans="5:11">
+      <c r="K8" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11"/>
+    </row>
+    <row r="9" spans="5:13">
       <c r="E9" s="11" t="s">
         <v>95</v>
       </c>
@@ -3388,11 +3451,17 @@
       <c r="J9" s="11">
         <v>0</v>
       </c>
-      <c r="K9" s="11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="5:11" ht="37.5">
+      <c r="K9" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="5:13" ht="37.5">
       <c r="E10" s="11" t="s">
         <v>96</v>
       </c>
@@ -3411,11 +3480,17 @@
       <c r="J10" s="11">
         <v>0</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="11">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="5:11" ht="37.5">
+    <row r="11" spans="5:13" ht="37.5">
       <c r="E11" s="11" t="s">
         <v>107</v>
       </c>
@@ -3434,11 +3509,17 @@
       <c r="J11" s="11">
         <v>0</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="K11" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L11" s="11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="5:11" ht="37.5">
+    <row r="12" spans="5:13" ht="37.5">
       <c r="E12" s="11" t="s">
         <v>114</v>
       </c>
@@ -3457,11 +3538,17 @@
       <c r="J12" s="11">
         <v>0</v>
       </c>
-      <c r="K12" s="12" t="s">
+      <c r="K12" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L12" s="11">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="5:11">
+    <row r="13" spans="5:13">
       <c r="E13" s="11" t="s">
         <v>117</v>
       </c>
@@ -3481,10 +3568,16 @@
         <v>0</v>
       </c>
       <c r="K13" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L13" s="11">
+        <v>0</v>
+      </c>
+      <c r="M13" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="5:11">
+    <row r="14" spans="5:13">
       <c r="E14" s="11" t="s">
         <v>119</v>
       </c>
@@ -3494,21 +3587,37 @@
       <c r="G14" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-    </row>
-    <row r="15" spans="5:11">
-      <c r="E15" s="11"/>
+      <c r="H14" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L14" s="13">
+        <v>1</v>
+      </c>
+      <c r="M14" s="11"/>
+    </row>
+    <row r="15" spans="5:13">
+      <c r="E15" s="11" t="s">
+        <v>123</v>
+      </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
-    </row>
-    <row r="16" spans="5:11">
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+    </row>
+    <row r="16" spans="5:13">
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
@@ -3516,8 +3625,10 @@
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
-    </row>
-    <row r="17" spans="5:11">
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+    </row>
+    <row r="17" spans="5:13">
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
@@ -3525,8 +3636,10 @@
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
-    </row>
-    <row r="18" spans="5:11">
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+    </row>
+    <row r="18" spans="5:13">
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -3534,8 +3647,10 @@
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
-    </row>
-    <row r="19" spans="5:11">
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+    </row>
+    <row r="19" spans="5:13">
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -3543,8 +3658,10 @@
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
-    </row>
-    <row r="20" spans="5:11">
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+    </row>
+    <row r="20" spans="5:13">
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
@@ -3552,8 +3669,10 @@
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
-    </row>
-    <row r="21" spans="5:11">
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+    </row>
+    <row r="21" spans="5:13">
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
       <c r="G21" s="11"/>
@@ -3561,8 +3680,10 @@
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
-    </row>
-    <row r="22" spans="5:11">
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+    </row>
+    <row r="22" spans="5:13">
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="11"/>
@@ -3570,8 +3691,10 @@
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
-    </row>
-    <row r="23" spans="5:11">
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" spans="5:13">
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
@@ -3579,8 +3702,10 @@
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
-    </row>
-    <row r="24" spans="5:11">
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+    </row>
+    <row r="24" spans="5:13">
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
@@ -3588,8 +3713,10 @@
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
-    </row>
-    <row r="25" spans="5:11">
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+    </row>
+    <row r="25" spans="5:13">
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
@@ -3597,8 +3724,10 @@
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
-    </row>
-    <row r="26" spans="5:11">
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+    </row>
+    <row r="26" spans="5:13">
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
@@ -3606,6 +3735,8 @@
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/Documents/仕様書.xlsx
+++ b/Documents/仕様書.xlsx
@@ -5,20 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2316012\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2316012\Documents\AvilityProject\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772BDD34-8DA6-4679-9C7A-27BEBD28D2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D0DC760-FB62-43DE-8A0A-6F5A48BF8A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="1" r:id="rId1"/>
     <sheet name="アビリティ" sheetId="5" r:id="rId2"/>
-    <sheet name="プレイヤー操作" sheetId="6" r:id="rId3"/>
-    <sheet name="クラス図" sheetId="4" r:id="rId4"/>
-    <sheet name="ステージ構成" sheetId="2" r:id="rId5"/>
-    <sheet name="画面遷移" sheetId="3" r:id="rId6"/>
+    <sheet name="パラメータ関係" sheetId="7" r:id="rId3"/>
+    <sheet name="プレイヤー操作" sheetId="6" r:id="rId4"/>
+    <sheet name="クラス図" sheetId="4" r:id="rId5"/>
+    <sheet name="ステージ構成" sheetId="2" r:id="rId6"/>
+    <sheet name="画面遷移" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="125">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -353,9 +354,6 @@
     <t>↑↓←→</t>
   </si>
   <si>
-    <t>X+左パッド</t>
-  </si>
-  <si>
     <t>地面に向かって勢いよく落ちる。</t>
   </si>
   <si>
@@ -392,12 +390,6 @@
     <t>「テレポート」を獲得すると可能</t>
   </si>
   <si>
-    <t>Eを押すと消え、離すと現れる。押してる間にW,A,S,Dで移動が可能。</t>
-  </si>
-  <si>
-    <t>Xを押すと消え、離すと現れる。押してる間に左パッドで移動が可能。</t>
-  </si>
-  <si>
     <t>ジャンプしたときに衝撃波を2つ放つ。</t>
   </si>
   <si>
@@ -413,13 +405,262 @@
     <t>「ボックス」を獲得すると可能</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
     <t>https://miro.com/app/live-embed/uXjVGj5v6-4=/?moveToViewport=-2715%2C-2146%2C6062%2C2819&amp;embedId=110213163200</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：スタンプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：ボックス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー(Lv.1)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー(Lv.2)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー(Lv.3)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力上昇率</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ジョウショウリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵：クローン</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加攻撃値</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>コウゲキアタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのステータスに加える</t>
+    <rPh sb="12" eb="13">
+      <t>クワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：ショット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>種類</t>
+    <rPh sb="0" eb="2">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オブジェクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>能力</t>
+    <rPh sb="0" eb="2">
+      <t>ノウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>基礎ステータスが上昇する</t>
+    <rPh sb="0" eb="2">
+      <t>キソ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのステータスに加える
+壁に反射するたびに攻撃力上昇率を0.1%ずつ上げていく</t>
+    <rPh sb="12" eb="13">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハンシャ</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="28" eb="31">
+      <t>ジョウショウリツ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：エアースラッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>飛び道具</t>
+    <rPh sb="0" eb="1">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ドウグ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのステータスに加える
+ダメージはプレイヤーの攻撃力から参照する</t>
+    <rPh sb="12" eb="13">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：テレポート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オブジェクト：キャラクターか敵、
+能力：アビリティ、
+飛び道具：魔法系の攻撃</t>
+    <rPh sb="14" eb="15">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ドウグ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ケイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：メタル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重力</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重力上昇率</t>
+    <rPh sb="0" eb="5">
+      <t>ジュウリョクジョウショウリツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤーのステータスに一時的に加える</t>
+    <rPh sb="12" eb="15">
+      <t>イチジテキ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>クワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X+左パッド下</t>
+    <rPh sb="6" eb="7">
+      <t>シタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E+S</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中にいるときにB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A+左パッド下を押すと消え、離すと現れる。押してる間に左パッドで移動が可能。</t>
+    <rPh sb="2" eb="3">
+      <t>ヒダリ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>シタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lshift+S</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ZR,ZL,R,L+左パッド</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -427,7 +668,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -455,6 +696,15 @@
       <color theme="0"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -490,7 +740,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -513,13 +763,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -546,6 +811,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -3003,6 +3280,490 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24BB326-7754-4978-971A-09FA9DBDB891}">
+  <dimension ref="E2:M26"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="2" max="2" width="8.125" customWidth="1"/>
+    <col min="3" max="3" width="8.875" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="36.625" customWidth="1"/>
+    <col min="8" max="8" width="9.375" customWidth="1"/>
+    <col min="9" max="9" width="10.75" customWidth="1"/>
+    <col min="10" max="12" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="53.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="5:13" ht="34.5" customHeight="1"/>
+    <row r="3" spans="5:13" ht="56.25">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" spans="5:13">
+      <c r="E4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="5:13">
+      <c r="E5" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="11">
+        <v>100</v>
+      </c>
+      <c r="H5" s="11">
+        <v>50</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0</v>
+      </c>
+      <c r="J5" s="11">
+        <v>0</v>
+      </c>
+      <c r="K5" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L5" s="11">
+        <v>0</v>
+      </c>
+      <c r="M5" s="11"/>
+    </row>
+    <row r="6" spans="5:13">
+      <c r="E6" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G6" s="11">
+        <v>140</v>
+      </c>
+      <c r="H6" s="11">
+        <v>70</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0</v>
+      </c>
+      <c r="J6" s="11">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L6" s="11">
+        <v>0</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="5:13">
+      <c r="E7" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="11">
+        <v>180</v>
+      </c>
+      <c r="H7" s="11">
+        <v>90</v>
+      </c>
+      <c r="I7" s="11">
+        <v>0</v>
+      </c>
+      <c r="J7" s="11">
+        <v>0</v>
+      </c>
+      <c r="K7" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="5:13">
+      <c r="E8" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="11">
+        <v>75</v>
+      </c>
+      <c r="H8" s="11">
+        <v>10</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0</v>
+      </c>
+      <c r="K8" s="11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11"/>
+    </row>
+    <row r="9" spans="5:13">
+      <c r="E9" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" s="11">
+        <v>50</v>
+      </c>
+      <c r="J9" s="11">
+        <v>0</v>
+      </c>
+      <c r="K9" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="5:13" ht="37.5">
+      <c r="E10" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10" s="11">
+        <v>1</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <v>100</v>
+      </c>
+      <c r="J10" s="11">
+        <v>0</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L10" s="11">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="5:13" ht="37.5">
+      <c r="E11" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I11" s="11">
+        <v>20</v>
+      </c>
+      <c r="J11" s="11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L11" s="11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="5:13" ht="37.5">
+      <c r="E12" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" s="11">
+        <v>30</v>
+      </c>
+      <c r="J12" s="11">
+        <v>0</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="11">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="5:13">
+      <c r="E13" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="11">
+        <v>30</v>
+      </c>
+      <c r="J13" s="11">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L13" s="11">
+        <v>0</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="5:13">
+      <c r="E14" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="L14" s="13">
+        <v>1</v>
+      </c>
+      <c r="M14" s="11"/>
+    </row>
+    <row r="15" spans="5:13">
+      <c r="E15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+    </row>
+    <row r="16" spans="5:13">
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+    </row>
+    <row r="17" spans="5:13">
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+    </row>
+    <row r="18" spans="5:13">
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+    </row>
+    <row r="19" spans="5:13">
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+    </row>
+    <row r="20" spans="5:13">
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="11"/>
+    </row>
+    <row r="21" spans="5:13">
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="11"/>
+    </row>
+    <row r="22" spans="5:13">
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" spans="5:13">
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="11"/>
+    </row>
+    <row r="24" spans="5:13">
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+    </row>
+    <row r="25" spans="5:13">
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+    </row>
+    <row r="26" spans="5:13">
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E95FD20-A5A3-4B15-92BD-87102E0D51C4}">
   <dimension ref="D4:H19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3113,7 +3874,7 @@
         <v>71</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="4:8">
@@ -3121,16 +3882,16 @@
         <v>21</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="11" spans="4:8">
@@ -3138,16 +3899,16 @@
         <v>24</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="12" spans="4:8">
@@ -3155,16 +3916,16 @@
         <v>26</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="4:8" ht="37.5">
@@ -3172,16 +3933,16 @@
         <v>29</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="G13" s="2" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="4:8">
@@ -3189,10 +3950,10 @@
         <v>32</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>62</v>
@@ -3203,19 +3964,19 @@
     </row>
     <row r="15" spans="4:8" ht="37.5">
       <c r="D15" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="4:8">
@@ -3254,7 +4015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53FD8591-C896-4DE4-A6F4-2E97EA0E58D4}">
   <dimension ref="C6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3264,7 +4025,7 @@
   <sheetData>
     <row r="6" spans="3:3">
       <c r="C6" s="9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3277,7 +4038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63FD3BE4-D508-4233-B771-14B3707C8539}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3287,7 +4048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44CE8C6D-A5D9-4296-ADEE-7D23BF1A189A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3299,6 +4060,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896">
@@ -3307,15 +4077,6 @@
     <TaxCatchAll xmlns="4df1b71f-4a55-4669-b731-80afe8527666" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3500,20 +4261,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44FA154F-6742-4FF5-B2DD-F9D58013581C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
     <ds:schemaRef ds:uri="4df1b71f-4a55-4669-b731-80afe8527666"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Documents/仕様書.xlsx
+++ b/Documents/仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2316012\Documents\AvilityProject\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D49336-8EDE-4A03-84E0-0D6A9D755173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7474DD77-B89A-45A7-A1A4-6F80084DBAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5265" yWindow="4185" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="111">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -173,42 +173,24 @@
 ⑤リザルト画面。順位を表示。ステージセレクトに戻る。</t>
   </si>
   <si>
-    <t>値は要調整</t>
-  </si>
-  <si>
-    <t>同じ番号のものは同時にもてない</t>
-  </si>
-  <si>
     <t>名前</t>
   </si>
   <si>
     <t>特徴</t>
   </si>
   <si>
-    <t>効果</t>
-  </si>
-  <si>
-    <t>スロット</t>
-  </si>
-  <si>
     <t>グラビティ</t>
   </si>
   <si>
     <t>重力を操れる</t>
   </si>
   <si>
-    <t>重力方向をいつでも切り替えれる</t>
-  </si>
-  <si>
     <t>スタンプ</t>
   </si>
   <si>
     <t>下に勢いよく落っこちる</t>
   </si>
   <si>
-    <t>基本ダメージ2</t>
-  </si>
-  <si>
     <t>ショット</t>
   </si>
   <si>
@@ -221,64 +203,36 @@
     <t>空中を歩ける</t>
   </si>
   <si>
-    <t>ジャンプ回数+5</t>
-  </si>
-  <si>
     <t>テレポート</t>
   </si>
   <si>
     <t>瞬間移動ができる</t>
   </si>
   <si>
-    <t>400くらい指定した方向へ移動。指定しない場合はその場で解除する。基本ダメージ2</t>
-  </si>
-  <si>
     <t>エアースラッシュ</t>
   </si>
   <si>
     <t>ジャンプと同時に衝撃波を放つ</t>
   </si>
   <si>
-    <t>基本ダメージ2。生存秒数1.5秒</t>
-  </si>
-  <si>
     <t>ボックス</t>
   </si>
   <si>
     <t>爆弾入りの箱を作れる。</t>
   </si>
   <si>
-    <t>基本ダメージ2。最大生成数3個。箱自体の体力は1。</t>
-  </si>
-  <si>
     <t>スーパーマン</t>
   </si>
   <si>
     <t>身体能力がめっちゃ上がる</t>
   </si>
   <si>
-    <t>移動速度とジャンプ力が2倍</t>
-  </si>
-  <si>
     <t>ジャイアント</t>
   </si>
   <si>
     <t>体がでかくなる</t>
   </si>
   <si>
-    <t>攻撃力+2。このアビリティでしか壊せない岩がある。
-移動速度とジャンプ力が0.5倍</t>
-  </si>
-  <si>
-    <t>メタル</t>
-  </si>
-  <si>
-    <t>体がメタル化する</t>
-  </si>
-  <si>
-    <t>攻撃力+2。重力が1.2倍</t>
-  </si>
-  <si>
     <t>アクション名</t>
   </si>
   <si>
@@ -354,9 +308,6 @@
     <t>↑↓←→</t>
   </si>
   <si>
-    <t>X+左パッド</t>
-  </si>
-  <si>
     <t>地面に向かって勢いよく落ちる。</t>
   </si>
   <si>
@@ -366,21 +317,12 @@
     <t>空中にいるときにSpace</t>
   </si>
   <si>
-    <t>空中にいるときにB</t>
-  </si>
-  <si>
     <t>壁に向かって勢いよく吹っ飛ぶ。3回ぶつかると止まる。</t>
   </si>
   <si>
     <t>「ショット」を獲得すると可能</t>
   </si>
   <si>
-    <t>Eを離すと飛ぶ。押してる間に←→で角度調整</t>
-  </si>
-  <si>
-    <t>Xを離すと飛ぶ。押してる間に左パッドで角度調整</t>
-  </si>
-  <si>
     <t>ジャンプ回数が増える。最大5回まで。</t>
   </si>
   <si>
@@ -393,31 +335,10 @@
     <t>「テレポート」を獲得すると可能</t>
   </si>
   <si>
-    <t>Eを押すと消え、離すと現れる。押してる間にW,A,S,Dで移動が可能。</t>
-  </si>
-  <si>
-    <t>Xを押すと消え、離すと現れる。押してる間に左パッドで移動が可能。</t>
-  </si>
-  <si>
     <t>ジャンプしたときに衝撃波を2つ放つ。</t>
   </si>
   <si>
     <t>「エアースラッシュ」を獲得すると可能</t>
-  </si>
-  <si>
-    <t>箱だし</t>
-  </si>
-  <si>
-    <t>箱を生成する。最大3つまで。壊れると爆発する。4つ目を生成しようとすると最も古い奴が爆発する</t>
-  </si>
-  <si>
-    <t>「ボックス」を獲得すると可能</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>X</t>
   </si>
   <si>
     <t>https://miro.com/app/live-embed/uXjVGj5v6-4=/?moveToViewport=-2715%2C-2146%2C6062%2C2819&amp;embedId=110213163200</t>
@@ -642,7 +563,104 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アビリティ：</t>
+    <t>B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空中にいるときにB</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>右スティック</t>
+    <rPh sb="0" eb="1">
+      <t>ミギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レーザー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3段階のレーザーを放てる</t>
+    <rPh sb="1" eb="3">
+      <t>ダンカイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アビリティ：レーザー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レーザーを放つ。チャージで3段階のビームを放てる</t>
+    <rPh sb="5" eb="6">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ダンカイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ハナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>「レーザー」を獲得すると可能</t>
+    <rPh sb="7" eb="9">
+      <t>カクトク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>E長押しでチャージ。離すと発射。</t>
+    <rPh sb="1" eb="3">
+      <t>ナガオ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハッシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>X長押しでチャージ。離すと発射。</t>
+    <rPh sb="1" eb="3">
+      <t>ナガオ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハッシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>W+Eを押すと消え、離すと現れる。押してる間にW,A,S,Dで移動が可能。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左スティック↑+Xを押すと消え、離すと現れる。押してる間に左パッドで移動が可能。</t>
+    <rPh sb="0" eb="1">
+      <t>ヒダリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S+Eを離すと飛ぶ。押してる間に←→で角度調整</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>左スティック↓+Xを離すと飛ぶ。押してる間に左パッドで角度調整</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -766,7 +784,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -782,9 +800,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -836,7 +851,7 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2989,92 +3004,92 @@
   </cols>
   <sheetData>
     <row r="4" spans="4:5">
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="4:5">
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="4:5">
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="4:5">
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="4:5" ht="165" customHeight="1">
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="4:5" ht="150" customHeight="1">
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="4:5">
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="4:5">
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="4:5">
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" spans="4:5">
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="4:5">
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="4:5">
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" spans="4:5">
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="4:5">
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
     </row>
     <row r="18" spans="4:5">
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" spans="4:5">
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3085,174 +3100,99 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97D56037-4ED5-4316-8A0E-3529C59D86FA}">
-  <dimension ref="F5:I16"/>
+  <dimension ref="F6:G16"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="6" max="6" width="22.5" customWidth="1"/>
     <col min="7" max="7" width="43.125" customWidth="1"/>
-    <col min="8" max="8" width="44.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="6:9">
-      <c r="H5" t="s">
+    <row r="6" spans="6:7">
+      <c r="F6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I5" t="s">
+      <c r="G6" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="6:9">
-      <c r="F6" s="4" t="s">
+    <row r="7" spans="6:7">
+      <c r="F7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="4" t="s">
+    </row>
+    <row r="8" spans="6:7">
+      <c r="F8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="6:9">
-      <c r="F7" s="5" t="s">
+    <row r="9" spans="6:7">
+      <c r="F9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="5" t="s">
+    </row>
+    <row r="10" spans="6:7">
+      <c r="F10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="6:9">
-      <c r="F8" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="5" t="s">
+    </row>
+    <row r="11" spans="6:7">
+      <c r="F11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="6:9">
-      <c r="F9" s="5" t="s">
+    </row>
+    <row r="12" spans="6:7">
+      <c r="F12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="6:9">
-      <c r="F10" s="5" t="s">
+    </row>
+    <row r="13" spans="6:7">
+      <c r="F13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="5" t="s">
+    </row>
+    <row r="14" spans="6:7">
+      <c r="F14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="6:9" ht="37.5">
-      <c r="F11" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="5" t="s">
+    </row>
+    <row r="15" spans="6:7">
+      <c r="F15" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="6:9">
-      <c r="F12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="6:9">
-      <c r="F13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="6:9">
-      <c r="F14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I14" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="6:9" ht="56.25">
-      <c r="F15" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="6:9">
+    </row>
+    <row r="16" spans="6:7">
       <c r="F16" s="5" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="5">
-        <v>3</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3279,464 +3219,478 @@
   <sheetData>
     <row r="2" spans="5:13" ht="34.5" customHeight="1"/>
     <row r="3" spans="5:13" ht="56.25">
-      <c r="E3" s="7"/>
-      <c r="F3" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
     </row>
     <row r="4" spans="5:13">
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="J4" s="10" t="s">
+      <c r="F4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="5:13">
+      <c r="E5" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="10">
+        <v>100</v>
+      </c>
+      <c r="H5" s="10">
+        <v>50</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0</v>
+      </c>
+      <c r="J5" s="10">
+        <v>0</v>
+      </c>
+      <c r="K5" s="10">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L5" s="10">
+        <v>0</v>
+      </c>
+      <c r="M5" s="10"/>
+    </row>
+    <row r="6" spans="5:13">
+      <c r="E6" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="10">
+        <v>140</v>
+      </c>
+      <c r="H6" s="10">
+        <v>70</v>
+      </c>
+      <c r="I6" s="10">
+        <v>0</v>
+      </c>
+      <c r="J6" s="10">
+        <v>0</v>
+      </c>
+      <c r="K6" s="10">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L6" s="10">
+        <v>0</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="5:13">
+      <c r="E7" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="10">
+        <v>180</v>
+      </c>
+      <c r="H7" s="10">
+        <v>90</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="5:13">
+      <c r="E8" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="10">
+        <v>75</v>
+      </c>
+      <c r="H8" s="10">
+        <v>10</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10"/>
+    </row>
+    <row r="9" spans="5:13">
+      <c r="E9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="10">
+        <v>50</v>
+      </c>
+      <c r="J9" s="10">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10">
+        <v>25.8</v>
+      </c>
+      <c r="L9" s="10">
+        <v>0</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="5:13" ht="37.5">
+      <c r="E10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10">
+        <v>100</v>
+      </c>
+      <c r="J10" s="10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="5:13" ht="37.5">
+      <c r="E11" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="10">
+        <v>20</v>
+      </c>
+      <c r="J11" s="10">
+        <v>0</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="5:13" ht="37.5">
+      <c r="E12" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="10">
+        <v>30</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="5:13">
+      <c r="E13" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="10">
+        <v>30</v>
+      </c>
+      <c r="J13" s="10">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="5:13">
+      <c r="E14" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" s="10">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L14" s="12">
+        <v>1</v>
+      </c>
+      <c r="M14" s="10"/>
+    </row>
+    <row r="15" spans="5:13" ht="37.5">
+      <c r="E15" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="K4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="5:13">
-      <c r="E5" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="11">
-        <v>100</v>
-      </c>
-      <c r="H5" s="11">
-        <v>50</v>
-      </c>
-      <c r="I5" s="11">
+      <c r="F15" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" s="10">
+        <v>30</v>
+      </c>
+      <c r="J15" s="10">
         <v>0</v>
       </c>
-      <c r="J5" s="11">
+      <c r="K15" s="10"/>
+      <c r="L15" s="10">
         <v>0</v>
       </c>
-      <c r="K5" s="11">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="L5" s="11">
-        <v>0</v>
-      </c>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" spans="5:13">
-      <c r="E6" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="11">
-        <v>140</v>
-      </c>
-      <c r="H6" s="11">
-        <v>70</v>
-      </c>
-      <c r="I6" s="11">
-        <v>0</v>
-      </c>
-      <c r="J6" s="11">
-        <v>0</v>
-      </c>
-      <c r="K6" s="11">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="L6" s="11">
-        <v>0</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="5:13">
-      <c r="E7" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G7" s="11">
-        <v>180</v>
-      </c>
-      <c r="H7" s="11">
+      <c r="M15" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="I7" s="11">
-        <v>0</v>
-      </c>
-      <c r="J7" s="11">
-        <v>0</v>
-      </c>
-      <c r="K7" s="11">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="L7" s="11">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="5:13">
-      <c r="E8" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G8" s="11">
-        <v>75</v>
-      </c>
-      <c r="H8" s="11">
-        <v>10</v>
-      </c>
-      <c r="I8" s="11">
-        <v>0</v>
-      </c>
-      <c r="J8" s="11">
-        <v>0</v>
-      </c>
-      <c r="K8" s="11">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="L8" s="11">
-        <v>0</v>
-      </c>
-      <c r="M8" s="11"/>
-    </row>
-    <row r="9" spans="5:13">
-      <c r="E9" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="I9" s="11">
-        <v>50</v>
-      </c>
-      <c r="J9" s="11">
-        <v>0</v>
-      </c>
-      <c r="K9" s="11">
-        <v>25.8</v>
-      </c>
-      <c r="L9" s="11">
-        <v>0</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="5:13" ht="37.5">
-      <c r="E10" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="11">
-        <v>1</v>
-      </c>
-      <c r="H10" s="11">
-        <v>0</v>
-      </c>
-      <c r="I10" s="11">
-        <v>100</v>
-      </c>
-      <c r="J10" s="11">
-        <v>0</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="L10" s="11">
-        <v>0</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="5:13" ht="37.5">
-      <c r="E11" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="I11" s="11">
-        <v>20</v>
-      </c>
-      <c r="J11" s="11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="L11" s="11">
-        <v>0</v>
-      </c>
-      <c r="M11" s="12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="5:13" ht="37.5">
-      <c r="E12" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="I12" s="11">
-        <v>30</v>
-      </c>
-      <c r="J12" s="11">
-        <v>0</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="L12" s="11">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="5:13">
-      <c r="E13" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" s="11">
-        <v>30</v>
-      </c>
-      <c r="J13" s="11">
-        <v>0</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="L13" s="11">
-        <v>0</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="5:13">
-      <c r="E14" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="I14" s="11">
-        <v>0</v>
-      </c>
-      <c r="J14" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="L14" s="13">
-        <v>1</v>
-      </c>
-      <c r="M14" s="11"/>
-    </row>
-    <row r="15" spans="5:13">
-      <c r="E15" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
     </row>
     <row r="16" spans="5:13">
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
     </row>
     <row r="17" spans="5:13">
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
     </row>
     <row r="18" spans="5:13">
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
     </row>
     <row r="19" spans="5:13">
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
     </row>
     <row r="20" spans="5:13">
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
     </row>
     <row r="21" spans="5:13">
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
     </row>
     <row r="22" spans="5:13">
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
     </row>
     <row r="23" spans="5:13">
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
     </row>
     <row r="24" spans="5:13">
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
     </row>
     <row r="25" spans="5:13">
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
     </row>
     <row r="26" spans="5:13">
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3747,218 +3701,218 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E95FD20-A5A3-4B15-92BD-87102E0D51C4}">
-  <dimension ref="D4:H19"/>
+  <dimension ref="D4:H18"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="4" max="4" width="15.375" customWidth="1"/>
     <col min="5" max="5" width="53.625" customWidth="1"/>
     <col min="6" max="6" width="49.125" customWidth="1"/>
-    <col min="7" max="7" width="39.5" customWidth="1"/>
-    <col min="8" max="8" width="43.75" customWidth="1"/>
+    <col min="7" max="7" width="43.875" customWidth="1"/>
+    <col min="8" max="8" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="4:8">
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="4:8">
       <c r="D5" s="3" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="4:8">
       <c r="D6" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="4:8">
       <c r="D7" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="4:8">
       <c r="D8" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="4:8">
       <c r="D9" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="4:8">
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="4:8">
       <c r="D11" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="4:8">
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="4:8" ht="37.5">
       <c r="D13" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="4:8">
       <c r="D14" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="4:8" ht="37.5">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="4:8">
       <c r="D15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="4:8">
@@ -3981,13 +3935,6 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="4:8">
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4006,8 +3953,8 @@
   </cols>
   <sheetData>
     <row r="6" spans="3:3">
-      <c r="C6" s="9" t="s">
-        <v>94</v>
+      <c r="C6" s="8" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4042,6 +3989,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4df1b71f-4a55-4669-b731-80afe8527666" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A266895D3745634495530F4DE8F2682A" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="bc4232d39cbd51ad980f2da95d792baf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896" xmlns:ns3="4df1b71f-4a55-4669-b731-80afe8527666" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dce5d8306af64726948b5c30825d92f7" ns2:_="" ns3:_="">
     <xsd:import namespace="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
@@ -4222,27 +4189,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4df1b71f-4a55-4669-b731-80afe8527666" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44FA154F-6742-4FF5-B2DD-F9D58013581C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
+    <ds:schemaRef ds:uri="4df1b71f-4a55-4669-b731-80afe8527666"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4AFE8B2-255C-4B8A-97FA-8FA1BCDB4ABE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4259,23 +4225,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44FA154F-6742-4FF5-B2DD-F9D58013581C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
-    <ds:schemaRef ds:uri="4df1b71f-4a55-4669-b731-80afe8527666"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Documents/仕様書.xlsx
+++ b/Documents/仕様書.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2316012\Documents\AvilityProject\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oboro\Documents\ゲーム制作\GitHub\AvilityProject\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7474DD77-B89A-45A7-A1A4-6F80084DBAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A30C7FC-01DC-44F4-916A-C6ED05081B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,15 +35,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="129">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -663,12 +660,110 @@
     <t>左スティック↓+Xを離すと飛ぶ。押してる間に左パッドで角度調整</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>アビリティ選択(デバッグ用)</t>
+  </si>
+  <si>
+    <t>アビリティを選ぶ</t>
+  </si>
+  <si>
+    <t>←→</t>
+  </si>
+  <si>
+    <t>アビリティ決定(デバッグ用)</t>
+  </si>
+  <si>
+    <t>アビリティを決定</t>
+  </si>
+  <si>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>アビリティ上書き選択</t>
+  </si>
+  <si>
+    <t>アビリティの最大所持数が3つまでのため1つ選んで上書きする</t>
+  </si>
+  <si>
+    <t>4つ目のアビリティを獲得したとき</t>
+  </si>
+  <si>
+    <t>←↑→</t>
+  </si>
+  <si>
+    <t>新規参加</t>
+    <rPh sb="0" eb="2">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2P以降の参加</t>
+    <rPh sb="2" eb="4">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>接続したいPadを繋げる</t>
+    <rPh sb="0" eb="2">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ツナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不可</t>
+    <rPh sb="0" eb="2">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A+B同時押し</t>
+    <rPh sb="3" eb="6">
+      <t>ドウジオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>途中離脱</t>
+    <rPh sb="0" eb="4">
+      <t>トチュウリダツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2P以降の途中離脱</t>
+    <rPh sb="2" eb="4">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>トチュウリダツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>selectボタン長押し</t>
+    <rPh sb="9" eb="11">
+      <t>ナガオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -707,8 +802,16 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -737,6 +840,12 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -784,7 +893,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -798,7 +907,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -819,6 +928,12 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -851,7 +966,7 @@
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3701,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E95FD20-A5A3-4B15-92BD-87102E0D51C4}">
-  <dimension ref="D4:H18"/>
+  <dimension ref="D4:H32"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="4" max="4" width="15.375" customWidth="1"/>
@@ -3915,26 +4030,168 @@
         <v>106</v>
       </c>
     </row>
-    <row r="16" spans="4:8">
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="4:8">
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+    <row r="16" spans="4:8" ht="37.5">
+      <c r="D16" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8" ht="37.5">
+      <c r="D17" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="18" spans="4:8">
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="D18" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8">
+      <c r="D19" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8">
+      <c r="D20" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="4:8">
+      <c r="D21" s="13"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+    </row>
+    <row r="22" spans="4:8">
+      <c r="D22" s="13"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+    </row>
+    <row r="23" spans="4:8">
+      <c r="D23" s="13"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" spans="4:8">
+      <c r="D24" s="13"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+    </row>
+    <row r="25" spans="4:8">
+      <c r="D25" s="13"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+    </row>
+    <row r="26" spans="4:8">
+      <c r="D26" s="13"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+    </row>
+    <row r="27" spans="4:8">
+      <c r="D27" s="13"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+    </row>
+    <row r="28" spans="4:8">
+      <c r="D28" s="13"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29" spans="4:8">
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+    </row>
+    <row r="30" spans="4:8">
+      <c r="D30" s="13"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" spans="4:8">
+      <c r="D31" s="13"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+    </row>
+    <row r="32" spans="4:8">
+      <c r="D32" s="13"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3989,26 +4246,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4df1b71f-4a55-4669-b731-80afe8527666" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A266895D3745634495530F4DE8F2682A" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="bc4232d39cbd51ad980f2da95d792baf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896" xmlns:ns3="4df1b71f-4a55-4669-b731-80afe8527666" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dce5d8306af64726948b5c30825d92f7" ns2:_="" ns3:_="">
     <xsd:import namespace="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
@@ -4189,10 +4426,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4df1b71f-4a55-4669-b731-80afe8527666" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4AFE8B2-255C-4B8A-97FA-8FA1BCDB4ABE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
+    <ds:schemaRef ds:uri="4df1b71f-4a55-4669-b731-80afe8527666"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4209,20 +4477,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4AFE8B2-255C-4B8A-97FA-8FA1BCDB4ABE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
-    <ds:schemaRef ds:uri="4df1b71f-4a55-4669-b731-80afe8527666"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Documents/仕様書.xlsx
+++ b/Documents/仕様書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oboro\Documents\ゲーム制作\GitHub\AvilityProject\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2316012\Documents\AvilityProject\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A30C7FC-01DC-44F4-916A-C6ED05081B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A91638-B771-4424-852B-98C5F4112664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概要" sheetId="1" r:id="rId1"/>
@@ -35,12 +35,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="127">
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
@@ -49,10 +52,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ProjectAvility</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>概要</t>
     <rPh sb="0" eb="2">
       <t>ガイヨウ</t>
@@ -60,57 +59,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>最後に待つボスを倒すとクリア。ボス戦までの道中雑魚敵を倒してプレイヤーを強化したり、アビリティを獲得することができる。</t>
-    <rPh sb="0" eb="2">
-      <t>サイゴ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>マ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>タオ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>セン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ドウチュウ</t>
-    </rPh>
-    <rPh sb="23" eb="26">
-      <t>ザコテキ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>タオ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>キョウカ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>カクトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>コンセプト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>各アビリティがもたらす特殊なプレイヤーの操作体験が魅力</t>
-    <rPh sb="0" eb="1">
-      <t>カク</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>トクシュ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>タイケン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ミリョク</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -121,53 +70,8 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ダークで闇の世界観。主人公たちは攫われた親を救いに行く。</t>
-    <rPh sb="4" eb="5">
-      <t>ヤミ</t>
-    </rPh>
-    <rPh sb="6" eb="9">
-      <t>セカイカン</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>シュジンコウ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>サラ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>オヤ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>スク</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>イ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ゲームの流れ
 (クエスト)</t>
-  </si>
-  <si>
-    <t>①ステージを選ぶ
-②最初の能力を選ぶ
-③ゲーム開始。強制スクロールでステージを進む。
-④道中イベントやミッション用の扉が置いてある。クリアするとレベルアップやアビリティを獲得することができる。
-⑤最後までたどり着くとボス戦用の扉がある。
-⑥ボス戦。倒すとクリア。
-⑦リザルト画面。スコアやクリア時間を表示。ステージセレクトに戻る。</t>
-  </si>
-  <si>
-    <t>ゲームの流れ
-(バーサス)</t>
-  </si>
-  <si>
-    <t>①ステージを選ぶ
-②最初の能力を選ぶ
-③ゲーム開始。プレイヤー同士で戦いあう。
-④最後の一人になったらクリア。
-⑤リザルト画面。順位を表示。ステージセレクトに戻る。</t>
   </si>
   <si>
     <t>名前</t>
@@ -755,6 +659,149 @@
     <t>selectボタン長押し</t>
     <rPh sb="9" eb="11">
       <t>ナガオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LOOTRAIN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージの道中で拾ったり敵を倒したりしてお金を稼いでいく。</t>
+    <rPh sb="5" eb="7">
+      <t>ドウチュウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヒロ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タオ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カネ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>カセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>盗賊。汽車が自分たちのアジト。</t>
+    <rPh sb="0" eb="2">
+      <t>トウゾク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キシャ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>能力やアイテムを駆使してステージや敵などのギミック等を攻略していく。様々なアクションで敵と対決する点やどれだけ金額を稼げたかなどのスコア要素が面白い。</t>
+    <rPh sb="0" eb="2">
+      <t>ノウリョク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>クシ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>コウリャク</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>サマザマ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>タイケツ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>カセ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>オモシロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①モードを選ぶ。
+②電車に移る。買い物などが可能。左端に行くとゲーム開始。
+③ゲームシーン。強制スクロールでステージを進む。
+④道中イベントやミッション用の扉が置いてある。クリアすると宝箱が出現してお金やアイテムを獲得することができる。
+⑤最後までたどり着くとボス戦用の扉がある。
+⑥ボス戦。倒すとクリア。
+⑦リザルト画面。稼いだ金額が表示。モードに応じて次のシーンへ移る。</t>
+    <rPh sb="5" eb="6">
+      <t>エラ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>デンシャ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ウツ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カノウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ヒダリハシ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="92" eb="94">
+      <t>タカラバコ</t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="100" eb="101">
+      <t>カネ</t>
+    </rPh>
+    <rPh sb="162" eb="163">
+      <t>カセ</t>
+    </rPh>
+    <rPh sb="165" eb="167">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="175" eb="176">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="178" eb="179">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="184" eb="185">
+      <t>ウツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3111,7 +3158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D4:E19"/>
+  <dimension ref="D4:E18"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="4" max="4" width="13.125" customWidth="1"/>
@@ -3123,48 +3170,44 @@
         <v>0</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>1</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="4:5">
       <c r="D5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="4:5" ht="37.5">
+      <c r="D6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="4:5">
-      <c r="D6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>5</v>
+      <c r="E6" s="7" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="4:5">
       <c r="D7" s="6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>7</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="4:5" ht="165" customHeight="1">
       <c r="D8" s="7" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="4:5" ht="150" customHeight="1">
-      <c r="D9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>11</v>
-      </c>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="4:5">
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="4:5">
       <c r="D10" s="6"/>
@@ -3201,10 +3244,6 @@
     <row r="18" spans="4:5">
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="4:5">
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3224,90 +3263,90 @@
   <sheetData>
     <row r="6" spans="6:7">
       <c r="F6" s="4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="6:7">
       <c r="F7" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="6:7">
       <c r="F8" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="6:7">
       <c r="F9" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="6:7">
       <c r="F10" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="6:7">
       <c r="F11" s="5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="6:7">
       <c r="F12" s="5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="6:7">
       <c r="F13" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="6:7">
       <c r="F14" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="6:7">
       <c r="F15" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="6:7">
       <c r="F16" s="5" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3336,7 +3375,7 @@
     <row r="3" spans="5:13" ht="56.25">
       <c r="E3" s="6"/>
       <c r="F3" s="7" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -3351,36 +3390,36 @@
         <v>0</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G4" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M4" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="5" spans="5:13">
       <c r="E5" s="10" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G5" s="10">
         <v>100</v>
@@ -3404,10 +3443,10 @@
     </row>
     <row r="6" spans="5:13">
       <c r="E6" s="10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G6" s="10">
         <v>140</v>
@@ -3428,15 +3467,15 @@
         <v>0</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="5:13">
       <c r="E7" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G7" s="10">
         <v>180</v>
@@ -3457,15 +3496,15 @@
         <v>0</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="5:13">
       <c r="E8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="G8" s="10">
         <v>75</v>
@@ -3489,16 +3528,16 @@
     </row>
     <row r="9" spans="5:13">
       <c r="E9" s="10" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I9" s="10">
         <v>50</v>
@@ -3513,15 +3552,15 @@
         <v>0</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="5:13" ht="37.5">
       <c r="E10" s="10" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G10" s="10">
         <v>1</v>
@@ -3536,27 +3575,27 @@
         <v>0</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L10" s="10">
         <v>0</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="5:13" ht="37.5">
       <c r="E11" s="10" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I11" s="10">
         <v>20</v>
@@ -3565,27 +3604,27 @@
         <v>0</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L11" s="10">
         <v>0</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="5:13" ht="37.5">
       <c r="E12" s="10" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I12" s="10">
         <v>30</v>
@@ -3594,27 +3633,27 @@
         <v>0</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L12" s="10">
         <v>0</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="5:13">
       <c r="E13" s="10" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I13" s="10">
         <v>30</v>
@@ -3623,27 +3662,27 @@
         <v>0</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L13" s="10">
         <v>0</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="5:13">
       <c r="E14" s="10" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I14" s="10">
         <v>0</v>
@@ -3652,7 +3691,7 @@
         <v>0.5</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L14" s="12">
         <v>1</v>
@@ -3661,16 +3700,16 @@
     </row>
     <row r="15" spans="5:13" ht="37.5">
       <c r="E15" s="10" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I15" s="10">
         <v>30</v>
@@ -3683,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="5:13">
@@ -3828,285 +3867,285 @@
   <sheetData>
     <row r="4" spans="4:8">
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="4:8">
       <c r="D5" s="3" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="4:8">
       <c r="D6" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="4:8">
       <c r="D7" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="4:8">
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="4:8">
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="4:8">
       <c r="D10" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="4:8">
       <c r="D11" s="3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="4:8">
       <c r="D12" s="3" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="4:8" ht="37.5">
       <c r="D13" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="4:8">
       <c r="D14" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="4:8">
       <c r="D15" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="4:8" ht="37.5">
       <c r="D16" s="13" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="4:8" ht="37.5">
       <c r="D17" s="13" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="4:8">
       <c r="D18" s="14" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" spans="4:8">
       <c r="D19" s="13" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="4:8">
       <c r="D20" s="13" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F20" s="14"/>
       <c r="G20" s="14" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="4:8">
@@ -4211,7 +4250,7 @@
   <sheetData>
     <row r="6" spans="3:3">
       <c r="C6" s="8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4246,6 +4285,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4df1b71f-4a55-4669-b731-80afe8527666" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A266895D3745634495530F4DE8F2682A" ma:contentTypeVersion="9" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="bc4232d39cbd51ad980f2da95d792baf">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896" xmlns:ns3="4df1b71f-4a55-4669-b731-80afe8527666" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dce5d8306af64726948b5c30825d92f7" ns2:_="" ns3:_="">
     <xsd:import namespace="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
@@ -4426,27 +4485,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4df1b71f-4a55-4669-b731-80afe8527666" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44FA154F-6742-4FF5-B2DD-F9D58013581C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
+    <ds:schemaRef ds:uri="4df1b71f-4a55-4669-b731-80afe8527666"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4AFE8B2-255C-4B8A-97FA-8FA1BCDB4ABE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4463,23 +4521,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44FA154F-6742-4FF5-B2DD-F9D58013581C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0a88d0bc-5ab5-4d65-9fb9-d221cccc0896"/>
-    <ds:schemaRef ds:uri="4df1b71f-4a55-4669-b731-80afe8527666"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{032E7F71-4576-4F87-8D0D-7F4E419A8410}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>